--- a/personal_trainer_forms/016_personal_training_par_q_form--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/016_personal_training_par_q_form--personal_trainer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5'8"</t>
+          <t>6'2_1/2"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5'8"</t>
+          <t>6'2 1/2"</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6'2_1/2"</t>
+          <t>6'4"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6'2 1/2"</t>
+          <t>6'4"</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6'4"</t>
+          <t>6'3/2"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6'4"</t>
+          <t>6'3/2"</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6'1/2"</t>
+          <t>5'7"</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6'1/2"</t>
+          <t>5'7"</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6'3/2"</t>
+          <t>6'6"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6'3/2"</t>
+          <t>6'6"</t>
         </is>
       </c>
     </row>
@@ -1352,63 +1352,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5'7"</t>
+          <t>5'6"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5'7"</t>
+          <t>5'6"</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>height_measurement_choices</t>
+          <t>weight_measurement_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6'6"</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6'6"</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>height_measurement_choices</t>
+          <t>weight_measurement_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6'5"</t>
+          <t>100_lbs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6'5"</t>
+          <t>100 lbs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>height_measurement_choices</t>
+          <t>weight_measurement_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5'6"</t>
+          <t>120_lbs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5'6"</t>
+          <t>120 lbs</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>140_lbs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>140 lbs</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100_lbs</t>
+          <t>150_lbs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>100 lbs</t>
+          <t>150 lbs</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>120_lbs</t>
+          <t>160_lbs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>120 lbs</t>
+          <t>160 lbs</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140_lbs</t>
+          <t>170_lbs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>140 lbs</t>
+          <t>170 lbs</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>150_lbs</t>
+          <t>180_lbs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>150 lbs</t>
+          <t>180 lbs</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>160_lbs</t>
+          <t>190_lbs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>160 lbs</t>
+          <t>190 lbs</t>
         </is>
       </c>
     </row>
@@ -1522,114 +1522,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>170_lbs</t>
+          <t>200_lbs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>170 lbs</t>
+          <t>200 lbs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>weight_measurement_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>180_lbs</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>180 lbs</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>weight_measurement_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>190_lbs</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>190 lbs</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>weight_measurement_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200_lbs</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>200 lbs</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>emergency_contact</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>emergency_contact</t>
+          <t>emergency contact</t>
         </is>
       </c>
     </row>
